--- a/Planning_previsionnel.xlsx
+++ b/Planning_previsionnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb7cb2bc8e575779/Documents/S8/Projet_Synthese_I4.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{A16BD7E3-6269-4344-8B20-BD5577407D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1092C164-707E-4355-B7FB-3B24D6EFD9A3}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{A16BD7E3-6269-4344-8B20-BD5577407D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26079B51-F341-40CF-9065-DA1390B2473B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t xml:space="preserve">Planning </t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Entrainement du modèle sélectionné</t>
+  </si>
+  <si>
+    <t>Redaction livrable intermediaire n°5</t>
   </si>
 </sst>
 </file>
@@ -423,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,7 +554,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
@@ -592,6 +595,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1291,7 +1295,7 @@
       <c r="Q10" s="54"/>
       <c r="R10" s="54"/>
       <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
+      <c r="T10" s="66"/>
       <c r="U10" s="48"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48"/>
@@ -1387,7 +1391,7 @@
       <c r="Q13" s="54"/>
       <c r="R13" s="54"/>
       <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
+      <c r="T13" s="66"/>
       <c r="U13" s="48"/>
       <c r="V13" s="48"/>
       <c r="W13" s="48"/>
@@ -1515,7 +1519,7 @@
       <c r="Q17" s="54"/>
       <c r="R17" s="54"/>
       <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
+      <c r="T17" s="66"/>
       <c r="U17" s="48"/>
       <c r="V17" s="48"/>
       <c r="W17" s="48"/>
@@ -1739,7 +1743,7 @@
       <c r="Q24" s="54"/>
       <c r="R24" s="54"/>
       <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
+      <c r="T24" s="66"/>
       <c r="U24" s="48"/>
       <c r="V24" s="48"/>
       <c r="W24" s="48"/>
@@ -1899,7 +1903,7 @@
       <c r="Q29" s="54"/>
       <c r="R29" s="54"/>
       <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
+      <c r="T29" s="66"/>
       <c r="U29" s="48"/>
       <c r="V29" s="48"/>
       <c r="W29" s="48"/>
@@ -1943,7 +1947,7 @@
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -2004,27 +2008,27 @@
       <c r="AB32" s="48"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
-      <c r="S33" s="13"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
       <c r="T33" s="47"/>
       <c r="U33" s="48"/>
       <c r="V33" s="48"/>

--- a/Planning_previsionnel.xlsx
+++ b/Planning_previsionnel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb7cb2bc8e575779/Documents/S8/Projet_Synthese_I4.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{A16BD7E3-6269-4344-8B20-BD5577407D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B02893E0-A211-4326-8179-1F2987E4F7B6}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{A16BD7E3-6269-4344-8B20-BD5577407D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F165997C-3069-4208-A6A2-8549308A6EBA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
   </bookViews>
@@ -550,14 +550,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -604,6 +598,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -939,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A9F773-746E-4B84-AB16-4A78A439CD53}">
-  <dimension ref="A1:AB380"/>
+  <dimension ref="A1:AQ380"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.33203125" style="9" customWidth="1"/>
@@ -948,8 +948,8 @@
     <col min="21" max="40" width="4.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -981,17 +981,32 @@
         <v>5</v>
       </c>
       <c r="T1" s="2"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="64"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="A2" s="62"/>
       <c r="B2" s="4">
         <v>46132</v>
       </c>
@@ -1049,48 +1064,78 @@
       <c r="T2" s="5">
         <v>46182</v>
       </c>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="47"/>
-      <c r="AB2" s="47"/>
-    </row>
-    <row r="3" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="65" t="s">
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="45"/>
+    </row>
+    <row r="3" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="47"/>
-      <c r="Z3" s="47"/>
-      <c r="AA3" s="47"/>
-      <c r="AB3" s="47"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
@@ -1113,16 +1158,31 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="47"/>
-      <c r="W4" s="47"/>
-      <c r="X4" s="47"/>
-      <c r="Y4" s="47"/>
-      <c r="Z4" s="47"/>
-      <c r="AA4" s="47"/>
-      <c r="AB4" s="47"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U4" s="45"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="45"/>
+      <c r="Z4" s="45"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="45"/>
+      <c r="AC4" s="45"/>
+      <c r="AD4" s="45"/>
+      <c r="AE4" s="45"/>
+      <c r="AF4" s="45"/>
+      <c r="AG4" s="45"/>
+      <c r="AH4" s="45"/>
+      <c r="AI4" s="45"/>
+      <c r="AJ4" s="45"/>
+      <c r="AK4" s="45"/>
+      <c r="AL4" s="45"/>
+      <c r="AM4" s="45"/>
+      <c r="AN4" s="45"/>
+      <c r="AO4" s="45"/>
+      <c r="AP4" s="45"/>
+      <c r="AQ4" s="45"/>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
@@ -1145,16 +1205,31 @@
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="45"/>
+      <c r="AD5" s="45"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AQ5" s="45"/>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -1177,16 +1252,31 @@
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U6" s="45"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="45"/>
+      <c r="AA6" s="45"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="45"/>
+      <c r="AD6" s="45"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="45"/>
+      <c r="AJ6" s="45"/>
+      <c r="AK6" s="45"/>
+      <c r="AL6" s="45"/>
+      <c r="AM6" s="45"/>
+      <c r="AN6" s="45"/>
+      <c r="AO6" s="45"/>
+      <c r="AP6" s="45"/>
+      <c r="AQ6" s="45"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -1209,16 +1299,31 @@
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
-      <c r="AA7" s="47"/>
-      <c r="AB7" s="47"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
+      <c r="Z7" s="45"/>
+      <c r="AA7" s="45"/>
+      <c r="AB7" s="45"/>
+      <c r="AC7" s="45"/>
+      <c r="AD7" s="45"/>
+      <c r="AE7" s="45"/>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="45"/>
+      <c r="AH7" s="45"/>
+      <c r="AI7" s="45"/>
+      <c r="AJ7" s="45"/>
+      <c r="AK7" s="45"/>
+      <c r="AL7" s="45"/>
+      <c r="AM7" s="45"/>
+      <c r="AN7" s="45"/>
+      <c r="AO7" s="45"/>
+      <c r="AP7" s="45"/>
+      <c r="AQ7" s="45"/>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
@@ -1241,16 +1346,31 @@
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
-      <c r="U8" s="47"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="47"/>
-      <c r="X8" s="47"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
-      <c r="AA8" s="47"/>
-      <c r="AB8" s="47"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U8" s="45"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="45"/>
+      <c r="X8" s="45"/>
+      <c r="Y8" s="45"/>
+      <c r="Z8" s="45"/>
+      <c r="AA8" s="45"/>
+      <c r="AB8" s="45"/>
+      <c r="AC8" s="45"/>
+      <c r="AD8" s="45"/>
+      <c r="AE8" s="45"/>
+      <c r="AF8" s="45"/>
+      <c r="AG8" s="45"/>
+      <c r="AH8" s="45"/>
+      <c r="AI8" s="45"/>
+      <c r="AJ8" s="45"/>
+      <c r="AK8" s="45"/>
+      <c r="AL8" s="45"/>
+      <c r="AM8" s="45"/>
+      <c r="AN8" s="45"/>
+      <c r="AO8" s="45"/>
+      <c r="AP8" s="45"/>
+      <c r="AQ8" s="45"/>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
@@ -1273,48 +1393,78 @@
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
-      <c r="X9" s="47"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="47"/>
-      <c r="AB9" s="47"/>
-    </row>
-    <row r="10" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="66" t="s">
+      <c r="U9" s="45"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="45"/>
+      <c r="AP9" s="45"/>
+      <c r="AQ9" s="45"/>
+    </row>
+    <row r="10" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="47"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="45"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="45"/>
+      <c r="X10" s="45"/>
+      <c r="Y10" s="45"/>
+      <c r="Z10" s="45"/>
+      <c r="AA10" s="45"/>
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="45"/>
+      <c r="AD10" s="45"/>
+      <c r="AE10" s="45"/>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="45"/>
+      <c r="AH10" s="45"/>
+      <c r="AI10" s="45"/>
+      <c r="AJ10" s="45"/>
+      <c r="AK10" s="45"/>
+      <c r="AL10" s="45"/>
+      <c r="AM10" s="45"/>
+      <c r="AN10" s="45"/>
+      <c r="AO10" s="45"/>
+      <c r="AP10" s="45"/>
+      <c r="AQ10" s="45"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
@@ -1337,16 +1487,31 @@
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
-      <c r="AA11" s="47"/>
-      <c r="AB11" s="47"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U11" s="45"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="45"/>
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="45"/>
+      <c r="AD11" s="45"/>
+      <c r="AE11" s="45"/>
+      <c r="AF11" s="45"/>
+      <c r="AG11" s="45"/>
+      <c r="AH11" s="45"/>
+      <c r="AI11" s="45"/>
+      <c r="AJ11" s="45"/>
+      <c r="AK11" s="45"/>
+      <c r="AL11" s="45"/>
+      <c r="AM11" s="45"/>
+      <c r="AN11" s="45"/>
+      <c r="AO11" s="45"/>
+      <c r="AP11" s="45"/>
+      <c r="AQ11" s="45"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
@@ -1369,48 +1534,78 @@
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-    </row>
-    <row r="13" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="66" t="s">
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="45"/>
+      <c r="AA12" s="45"/>
+      <c r="AB12" s="45"/>
+      <c r="AC12" s="45"/>
+      <c r="AD12" s="45"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+    </row>
+    <row r="13" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="47"/>
-      <c r="AB13" s="47"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="61"/>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
+      <c r="W13" s="45"/>
+      <c r="X13" s="45"/>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="45"/>
+      <c r="AA13" s="45"/>
+      <c r="AB13" s="45"/>
+      <c r="AC13" s="45"/>
+      <c r="AD13" s="45"/>
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="45"/>
+      <c r="AH13" s="45"/>
+      <c r="AI13" s="45"/>
+      <c r="AJ13" s="45"/>
+      <c r="AK13" s="45"/>
+      <c r="AL13" s="45"/>
+      <c r="AM13" s="45"/>
+      <c r="AN13" s="45"/>
+      <c r="AO13" s="45"/>
+      <c r="AP13" s="45"/>
+      <c r="AQ13" s="45"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
@@ -1433,16 +1628,31 @@
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="47"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U14" s="45"/>
+      <c r="V14" s="45"/>
+      <c r="W14" s="45"/>
+      <c r="X14" s="45"/>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="45"/>
+      <c r="AA14" s="45"/>
+      <c r="AB14" s="45"/>
+      <c r="AC14" s="45"/>
+      <c r="AD14" s="45"/>
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="45"/>
+      <c r="AG14" s="45"/>
+      <c r="AH14" s="45"/>
+      <c r="AI14" s="45"/>
+      <c r="AJ14" s="45"/>
+      <c r="AK14" s="45"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="45"/>
+      <c r="AN14" s="45"/>
+      <c r="AO14" s="45"/>
+      <c r="AP14" s="45"/>
+      <c r="AQ14" s="45"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>18</v>
       </c>
@@ -1465,16 +1675,31 @@
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U15" s="45"/>
+      <c r="V15" s="45"/>
+      <c r="W15" s="45"/>
+      <c r="X15" s="45"/>
+      <c r="Y15" s="45"/>
+      <c r="Z15" s="45"/>
+      <c r="AA15" s="45"/>
+      <c r="AB15" s="45"/>
+      <c r="AC15" s="45"/>
+      <c r="AD15" s="45"/>
+      <c r="AE15" s="45"/>
+      <c r="AF15" s="45"/>
+      <c r="AG15" s="45"/>
+      <c r="AH15" s="45"/>
+      <c r="AI15" s="45"/>
+      <c r="AJ15" s="45"/>
+      <c r="AK15" s="45"/>
+      <c r="AL15" s="45"/>
+      <c r="AM15" s="45"/>
+      <c r="AN15" s="45"/>
+      <c r="AO15" s="45"/>
+      <c r="AP15" s="45"/>
+      <c r="AQ15" s="45"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
@@ -1497,48 +1722,78 @@
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="47"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="47"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="66" t="s">
+      <c r="U16" s="45"/>
+      <c r="V16" s="45"/>
+      <c r="W16" s="45"/>
+      <c r="X16" s="45"/>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="45"/>
+      <c r="AA16" s="45"/>
+      <c r="AB16" s="45"/>
+      <c r="AC16" s="45"/>
+      <c r="AD16" s="45"/>
+      <c r="AE16" s="45"/>
+      <c r="AF16" s="45"/>
+      <c r="AG16" s="45"/>
+      <c r="AH16" s="45"/>
+      <c r="AI16" s="45"/>
+      <c r="AJ16" s="45"/>
+      <c r="AK16" s="45"/>
+      <c r="AL16" s="45"/>
+      <c r="AM16" s="45"/>
+      <c r="AN16" s="45"/>
+      <c r="AO16" s="45"/>
+      <c r="AP16" s="45"/>
+      <c r="AQ16" s="45"/>
+    </row>
+    <row r="17" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="63"/>
-      <c r="U17" s="47"/>
-      <c r="V17" s="47"/>
-      <c r="W17" s="47"/>
-      <c r="X17" s="47"/>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="47"/>
-      <c r="AA17" s="47"/>
-      <c r="AB17" s="47"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="45"/>
+      <c r="V17" s="45"/>
+      <c r="W17" s="45"/>
+      <c r="X17" s="45"/>
+      <c r="Y17" s="45"/>
+      <c r="Z17" s="45"/>
+      <c r="AA17" s="45"/>
+      <c r="AB17" s="45"/>
+      <c r="AC17" s="45"/>
+      <c r="AD17" s="45"/>
+      <c r="AE17" s="45"/>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="45"/>
+      <c r="AH17" s="45"/>
+      <c r="AI17" s="45"/>
+      <c r="AJ17" s="45"/>
+      <c r="AK17" s="45"/>
+      <c r="AL17" s="45"/>
+      <c r="AM17" s="45"/>
+      <c r="AN17" s="45"/>
+      <c r="AO17" s="45"/>
+      <c r="AP17" s="45"/>
+      <c r="AQ17" s="45"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>20</v>
       </c>
@@ -1561,16 +1816,31 @@
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
-      <c r="U18" s="47"/>
-      <c r="V18" s="47"/>
-      <c r="W18" s="47"/>
-      <c r="X18" s="47"/>
-      <c r="Y18" s="47"/>
-      <c r="Z18" s="47"/>
-      <c r="AA18" s="47"/>
-      <c r="AB18" s="47"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U18" s="45"/>
+      <c r="V18" s="45"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="45"/>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="45"/>
+      <c r="AA18" s="45"/>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="45"/>
+      <c r="AE18" s="45"/>
+      <c r="AF18" s="45"/>
+      <c r="AG18" s="45"/>
+      <c r="AH18" s="45"/>
+      <c r="AI18" s="45"/>
+      <c r="AJ18" s="45"/>
+      <c r="AK18" s="45"/>
+      <c r="AL18" s="45"/>
+      <c r="AM18" s="45"/>
+      <c r="AN18" s="45"/>
+      <c r="AO18" s="45"/>
+      <c r="AP18" s="45"/>
+      <c r="AQ18" s="45"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>21</v>
       </c>
@@ -1593,16 +1863,31 @@
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="47"/>
-      <c r="AA19" s="47"/>
-      <c r="AB19" s="47"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U19" s="45"/>
+      <c r="V19" s="45"/>
+      <c r="W19" s="45"/>
+      <c r="X19" s="45"/>
+      <c r="Y19" s="45"/>
+      <c r="Z19" s="45"/>
+      <c r="AA19" s="45"/>
+      <c r="AB19" s="45"/>
+      <c r="AC19" s="45"/>
+      <c r="AD19" s="45"/>
+      <c r="AE19" s="45"/>
+      <c r="AF19" s="45"/>
+      <c r="AG19" s="45"/>
+      <c r="AH19" s="45"/>
+      <c r="AI19" s="45"/>
+      <c r="AJ19" s="45"/>
+      <c r="AK19" s="45"/>
+      <c r="AL19" s="45"/>
+      <c r="AM19" s="45"/>
+      <c r="AN19" s="45"/>
+      <c r="AO19" s="45"/>
+      <c r="AP19" s="45"/>
+      <c r="AQ19" s="45"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
@@ -1614,7 +1899,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="61"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="38"/>
       <c r="L20" s="34"/>
       <c r="M20" s="12"/>
@@ -1625,16 +1910,31 @@
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
-      <c r="U20" s="47"/>
-      <c r="V20" s="47"/>
-      <c r="W20" s="47"/>
-      <c r="X20" s="47"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="47"/>
-      <c r="AA20" s="47"/>
-      <c r="AB20" s="47"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U20" s="45"/>
+      <c r="V20" s="45"/>
+      <c r="W20" s="45"/>
+      <c r="X20" s="45"/>
+      <c r="Y20" s="45"/>
+      <c r="Z20" s="45"/>
+      <c r="AA20" s="45"/>
+      <c r="AB20" s="45"/>
+      <c r="AC20" s="45"/>
+      <c r="AD20" s="45"/>
+      <c r="AE20" s="45"/>
+      <c r="AF20" s="45"/>
+      <c r="AG20" s="45"/>
+      <c r="AH20" s="45"/>
+      <c r="AI20" s="45"/>
+      <c r="AJ20" s="45"/>
+      <c r="AK20" s="45"/>
+      <c r="AL20" s="45"/>
+      <c r="AM20" s="45"/>
+      <c r="AN20" s="45"/>
+      <c r="AO20" s="45"/>
+      <c r="AP20" s="45"/>
+      <c r="AQ20" s="45"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
@@ -1646,27 +1946,42 @@
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
       <c r="M21" s="36"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
-      <c r="U21" s="47"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
-      <c r="AA21" s="47"/>
-      <c r="AB21" s="47"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
+      <c r="W21" s="45"/>
+      <c r="X21" s="45"/>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="45"/>
+      <c r="AA21" s="45"/>
+      <c r="AB21" s="45"/>
+      <c r="AC21" s="45"/>
+      <c r="AD21" s="45"/>
+      <c r="AE21" s="45"/>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="45"/>
+      <c r="AH21" s="45"/>
+      <c r="AI21" s="45"/>
+      <c r="AJ21" s="45"/>
+      <c r="AK21" s="45"/>
+      <c r="AL21" s="45"/>
+      <c r="AM21" s="45"/>
+      <c r="AN21" s="45"/>
+      <c r="AO21" s="45"/>
+      <c r="AP21" s="45"/>
+      <c r="AQ21" s="45"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>33</v>
       </c>
@@ -1678,27 +1993,42 @@
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
       <c r="M22" s="36"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
-      <c r="U22" s="47"/>
-      <c r="V22" s="47"/>
-      <c r="W22" s="47"/>
-      <c r="X22" s="47"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="47"/>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="47"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U22" s="45"/>
+      <c r="V22" s="45"/>
+      <c r="W22" s="45"/>
+      <c r="X22" s="45"/>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="45"/>
+      <c r="AA22" s="45"/>
+      <c r="AB22" s="45"/>
+      <c r="AC22" s="45"/>
+      <c r="AD22" s="45"/>
+      <c r="AE22" s="45"/>
+      <c r="AF22" s="45"/>
+      <c r="AG22" s="45"/>
+      <c r="AH22" s="45"/>
+      <c r="AI22" s="45"/>
+      <c r="AJ22" s="45"/>
+      <c r="AK22" s="45"/>
+      <c r="AL22" s="45"/>
+      <c r="AM22" s="45"/>
+      <c r="AN22" s="45"/>
+      <c r="AO22" s="45"/>
+      <c r="AP22" s="45"/>
+      <c r="AQ22" s="45"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>27</v>
       </c>
@@ -1713,7 +2043,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="57"/>
+      <c r="M23" s="55"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -1721,48 +2051,78 @@
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
-      <c r="AA23" s="47"/>
-      <c r="AB23" s="47"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="66" t="s">
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
+      <c r="AA23" s="45"/>
+      <c r="AB23" s="45"/>
+      <c r="AC23" s="45"/>
+      <c r="AD23" s="45"/>
+      <c r="AE23" s="45"/>
+      <c r="AF23" s="45"/>
+      <c r="AG23" s="45"/>
+      <c r="AH23" s="45"/>
+      <c r="AI23" s="45"/>
+      <c r="AJ23" s="45"/>
+      <c r="AK23" s="45"/>
+      <c r="AL23" s="45"/>
+      <c r="AM23" s="45"/>
+      <c r="AN23" s="45"/>
+      <c r="AO23" s="45"/>
+      <c r="AP23" s="45"/>
+      <c r="AQ23" s="45"/>
+    </row>
+    <row r="24" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="47"/>
-      <c r="V24" s="47"/>
-      <c r="W24" s="47"/>
-      <c r="X24" s="47"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
-      <c r="AA24" s="47"/>
-      <c r="AB24" s="47"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="49"/>
+      <c r="R24" s="49"/>
+      <c r="S24" s="49"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="45"/>
+      <c r="X24" s="45"/>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="45"/>
+      <c r="AA24" s="45"/>
+      <c r="AB24" s="45"/>
+      <c r="AC24" s="45"/>
+      <c r="AD24" s="45"/>
+      <c r="AE24" s="45"/>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="45"/>
+      <c r="AH24" s="45"/>
+      <c r="AI24" s="45"/>
+      <c r="AJ24" s="45"/>
+      <c r="AK24" s="45"/>
+      <c r="AL24" s="45"/>
+      <c r="AM24" s="45"/>
+      <c r="AN24" s="45"/>
+      <c r="AO24" s="45"/>
+      <c r="AP24" s="45"/>
+      <c r="AQ24" s="45"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A25" s="37" t="s">
         <v>34</v>
       </c>
@@ -1776,8 +2136,8 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="54"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="52"/>
       <c r="N25" s="39"/>
       <c r="O25" s="39"/>
       <c r="P25" s="39"/>
@@ -1785,16 +2145,31 @@
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
-      <c r="U25" s="47"/>
-      <c r="V25" s="47"/>
-      <c r="W25" s="47"/>
-      <c r="X25" s="47"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="47"/>
-      <c r="AA25" s="47"/>
-      <c r="AB25" s="47"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U25" s="45"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="45"/>
+      <c r="X25" s="45"/>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="45"/>
+      <c r="AA25" s="45"/>
+      <c r="AB25" s="45"/>
+      <c r="AC25" s="45"/>
+      <c r="AD25" s="45"/>
+      <c r="AE25" s="45"/>
+      <c r="AF25" s="45"/>
+      <c r="AG25" s="45"/>
+      <c r="AH25" s="45"/>
+      <c r="AI25" s="45"/>
+      <c r="AJ25" s="45"/>
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="45"/>
+      <c r="AM25" s="45"/>
+      <c r="AN25" s="45"/>
+      <c r="AO25" s="45"/>
+      <c r="AP25" s="45"/>
+      <c r="AQ25" s="45"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -1810,23 +2185,38 @@
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="59"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="47"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="47"/>
-      <c r="AA26" s="47"/>
-      <c r="AB26" s="47"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="45"/>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="45"/>
+      <c r="AA26" s="45"/>
+      <c r="AB26" s="45"/>
+      <c r="AC26" s="45"/>
+      <c r="AD26" s="45"/>
+      <c r="AE26" s="45"/>
+      <c r="AF26" s="45"/>
+      <c r="AG26" s="45"/>
+      <c r="AH26" s="45"/>
+      <c r="AI26" s="45"/>
+      <c r="AJ26" s="45"/>
+      <c r="AK26" s="45"/>
+      <c r="AL26" s="45"/>
+      <c r="AM26" s="45"/>
+      <c r="AN26" s="45"/>
+      <c r="AO26" s="45"/>
+      <c r="AP26" s="45"/>
+      <c r="AQ26" s="45"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>26</v>
       </c>
@@ -1842,23 +2232,38 @@
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="51"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U27" s="45"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="X27" s="45"/>
+      <c r="Y27" s="45"/>
+      <c r="Z27" s="45"/>
+      <c r="AA27" s="45"/>
+      <c r="AB27" s="45"/>
+      <c r="AC27" s="45"/>
+      <c r="AD27" s="45"/>
+      <c r="AE27" s="45"/>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="45"/>
+      <c r="AH27" s="45"/>
+      <c r="AI27" s="45"/>
+      <c r="AJ27" s="45"/>
+      <c r="AK27" s="45"/>
+      <c r="AL27" s="45"/>
+      <c r="AM27" s="45"/>
+      <c r="AN27" s="45"/>
+      <c r="AO27" s="45"/>
+      <c r="AP27" s="45"/>
+      <c r="AQ27" s="45"/>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>30</v>
       </c>
@@ -1873,7 +2278,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
-      <c r="M28" s="61"/>
+      <c r="M28" s="59"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
@@ -1881,48 +2286,78 @@
       <c r="R28" s="41"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
-      <c r="U28" s="47"/>
-      <c r="V28" s="47"/>
-      <c r="W28" s="47"/>
-      <c r="X28" s="47"/>
-      <c r="Y28" s="47"/>
-      <c r="Z28" s="47"/>
-      <c r="AA28" s="47"/>
-      <c r="AB28" s="47"/>
-    </row>
-    <row r="29" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="45"/>
+      <c r="AB28" s="45"/>
+      <c r="AC28" s="45"/>
+      <c r="AD28" s="45"/>
+      <c r="AE28" s="45"/>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="45"/>
+      <c r="AH28" s="45"/>
+      <c r="AI28" s="45"/>
+      <c r="AJ28" s="45"/>
+      <c r="AK28" s="45"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="45"/>
+      <c r="AN28" s="45"/>
+      <c r="AO28" s="45"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+    </row>
+    <row r="29" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="63"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="47"/>
-      <c r="W29" s="47"/>
-      <c r="X29" s="47"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
-      <c r="AA29" s="47"/>
-      <c r="AB29" s="47"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="45"/>
+      <c r="X29" s="45"/>
+      <c r="Y29" s="45"/>
+      <c r="Z29" s="45"/>
+      <c r="AA29" s="45"/>
+      <c r="AB29" s="45"/>
+      <c r="AC29" s="45"/>
+      <c r="AD29" s="45"/>
+      <c r="AE29" s="45"/>
+      <c r="AF29" s="45"/>
+      <c r="AG29" s="45"/>
+      <c r="AH29" s="45"/>
+      <c r="AI29" s="45"/>
+      <c r="AJ29" s="45"/>
+      <c r="AK29" s="45"/>
+      <c r="AL29" s="45"/>
+      <c r="AM29" s="45"/>
+      <c r="AN29" s="45"/>
+      <c r="AO29" s="45"/>
+      <c r="AP29" s="45"/>
+      <c r="AQ29" s="45"/>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>29</v>
       </c>
@@ -1941,20 +2376,35 @@
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="62"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="60"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="47"/>
-      <c r="W30" s="47"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="47"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="47"/>
-      <c r="AB30" s="47"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
+      <c r="X30" s="45"/>
+      <c r="Y30" s="45"/>
+      <c r="Z30" s="45"/>
+      <c r="AA30" s="45"/>
+      <c r="AB30" s="45"/>
+      <c r="AC30" s="45"/>
+      <c r="AD30" s="45"/>
+      <c r="AE30" s="45"/>
+      <c r="AF30" s="45"/>
+      <c r="AG30" s="45"/>
+      <c r="AH30" s="45"/>
+      <c r="AI30" s="45"/>
+      <c r="AJ30" s="45"/>
+      <c r="AK30" s="45"/>
+      <c r="AL30" s="45"/>
+      <c r="AM30" s="45"/>
+      <c r="AN30" s="45"/>
+      <c r="AO30" s="45"/>
+      <c r="AP30" s="45"/>
+      <c r="AQ30" s="45"/>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>35</v>
       </c>
@@ -1972,19 +2422,34 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
-      <c r="R31" s="43"/>
+      <c r="R31" s="42"/>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
-      <c r="U31" s="47"/>
-      <c r="V31" s="47"/>
-      <c r="W31" s="47"/>
-      <c r="X31" s="47"/>
-      <c r="Y31" s="47"/>
-      <c r="Z31" s="47"/>
-      <c r="AA31" s="47"/>
-      <c r="AB31" s="47"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U31" s="45"/>
+      <c r="V31" s="45"/>
+      <c r="W31" s="45"/>
+      <c r="X31" s="45"/>
+      <c r="Y31" s="45"/>
+      <c r="Z31" s="45"/>
+      <c r="AA31" s="45"/>
+      <c r="AB31" s="45"/>
+      <c r="AC31" s="45"/>
+      <c r="AD31" s="45"/>
+      <c r="AE31" s="45"/>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="45"/>
+      <c r="AH31" s="45"/>
+      <c r="AI31" s="45"/>
+      <c r="AJ31" s="45"/>
+      <c r="AK31" s="45"/>
+      <c r="AL31" s="45"/>
+      <c r="AM31" s="45"/>
+      <c r="AN31" s="45"/>
+      <c r="AO31" s="45"/>
+      <c r="AP31" s="45"/>
+      <c r="AQ31" s="45"/>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>31</v>
       </c>
@@ -2003,20 +2468,35 @@
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
       <c r="P32" s="7"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="45"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="66"/>
       <c r="T32" s="7"/>
-      <c r="U32" s="47"/>
-      <c r="V32" s="47"/>
-      <c r="W32" s="47"/>
-      <c r="X32" s="47"/>
-      <c r="Y32" s="47"/>
-      <c r="Z32" s="47"/>
-      <c r="AA32" s="47"/>
-      <c r="AB32" s="47"/>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="45"/>
+      <c r="AD32" s="45"/>
+      <c r="AE32" s="45"/>
+      <c r="AF32" s="45"/>
+      <c r="AG32" s="45"/>
+      <c r="AH32" s="45"/>
+      <c r="AI32" s="45"/>
+      <c r="AJ32" s="45"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
+      <c r="AM32" s="45"/>
+      <c r="AN32" s="45"/>
+      <c r="AO32" s="45"/>
+      <c r="AP32" s="45"/>
+      <c r="AQ32" s="45"/>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>32</v>
       </c>
@@ -2038,17 +2518,32 @@
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="47"/>
-      <c r="AA33" s="47"/>
-      <c r="AB33" s="47"/>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="T33" s="44"/>
+      <c r="U33" s="45"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="45"/>
+      <c r="X33" s="45"/>
+      <c r="Y33" s="45"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="45"/>
+      <c r="AD33" s="45"/>
+      <c r="AE33" s="45"/>
+      <c r="AF33" s="45"/>
+      <c r="AG33" s="45"/>
+      <c r="AH33" s="45"/>
+      <c r="AI33" s="45"/>
+      <c r="AJ33" s="45"/>
+      <c r="AK33" s="45"/>
+      <c r="AL33" s="45"/>
+      <c r="AM33" s="45"/>
+      <c r="AN33" s="45"/>
+      <c r="AO33" s="45"/>
+      <c r="AP33" s="45"/>
+      <c r="AQ33" s="45"/>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -2069,16 +2564,31 @@
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="47"/>
-      <c r="AB34" s="47"/>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U34" s="45"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
+      <c r="X34" s="45"/>
+      <c r="Y34" s="45"/>
+      <c r="Z34" s="45"/>
+      <c r="AA34" s="45"/>
+      <c r="AB34" s="45"/>
+      <c r="AC34" s="45"/>
+      <c r="AD34" s="45"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="45"/>
+      <c r="AI34" s="45"/>
+      <c r="AJ34" s="45"/>
+      <c r="AK34" s="45"/>
+      <c r="AL34" s="45"/>
+      <c r="AM34" s="45"/>
+      <c r="AN34" s="45"/>
+      <c r="AO34" s="45"/>
+      <c r="AP34" s="45"/>
+      <c r="AQ34" s="45"/>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2099,16 +2609,31 @@
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
-      <c r="AA35" s="47"/>
-      <c r="AB35" s="47"/>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U35" s="45"/>
+      <c r="V35" s="45"/>
+      <c r="W35" s="45"/>
+      <c r="X35" s="45"/>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="45"/>
+      <c r="AA35" s="45"/>
+      <c r="AB35" s="45"/>
+      <c r="AC35" s="45"/>
+      <c r="AD35" s="45"/>
+      <c r="AE35" s="45"/>
+      <c r="AF35" s="45"/>
+      <c r="AG35" s="45"/>
+      <c r="AH35" s="45"/>
+      <c r="AI35" s="45"/>
+      <c r="AJ35" s="45"/>
+      <c r="AK35" s="45"/>
+      <c r="AL35" s="45"/>
+      <c r="AM35" s="45"/>
+      <c r="AN35" s="45"/>
+      <c r="AO35" s="45"/>
+      <c r="AP35" s="45"/>
+      <c r="AQ35" s="45"/>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -2129,16 +2654,31 @@
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
-      <c r="W36" s="47"/>
-      <c r="X36" s="47"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="47"/>
-      <c r="AA36" s="47"/>
-      <c r="AB36" s="47"/>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U36" s="45"/>
+      <c r="V36" s="45"/>
+      <c r="W36" s="45"/>
+      <c r="X36" s="45"/>
+      <c r="Y36" s="45"/>
+      <c r="Z36" s="45"/>
+      <c r="AA36" s="45"/>
+      <c r="AB36" s="45"/>
+      <c r="AC36" s="45"/>
+      <c r="AD36" s="45"/>
+      <c r="AE36" s="45"/>
+      <c r="AF36" s="45"/>
+      <c r="AG36" s="45"/>
+      <c r="AH36" s="45"/>
+      <c r="AI36" s="45"/>
+      <c r="AJ36" s="45"/>
+      <c r="AK36" s="45"/>
+      <c r="AL36" s="45"/>
+      <c r="AM36" s="45"/>
+      <c r="AN36" s="45"/>
+      <c r="AO36" s="45"/>
+      <c r="AP36" s="45"/>
+      <c r="AQ36" s="45"/>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -2159,16 +2699,31 @@
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
-      <c r="U37" s="47"/>
-      <c r="V37" s="47"/>
-      <c r="W37" s="47"/>
-      <c r="X37" s="47"/>
-      <c r="Y37" s="47"/>
-      <c r="Z37" s="47"/>
-      <c r="AA37" s="47"/>
-      <c r="AB37" s="47"/>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U37" s="45"/>
+      <c r="V37" s="45"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="45"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="45"/>
+      <c r="AB37" s="45"/>
+      <c r="AC37" s="45"/>
+      <c r="AD37" s="45"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="45"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="45"/>
+      <c r="AJ37" s="45"/>
+      <c r="AK37" s="45"/>
+      <c r="AL37" s="45"/>
+      <c r="AM37" s="45"/>
+      <c r="AN37" s="45"/>
+      <c r="AO37" s="45"/>
+      <c r="AP37" s="45"/>
+      <c r="AQ37" s="45"/>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -2189,16 +2744,31 @@
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
-      <c r="U38" s="47"/>
-      <c r="V38" s="47"/>
-      <c r="W38" s="47"/>
-      <c r="X38" s="47"/>
-      <c r="Y38" s="47"/>
-      <c r="Z38" s="47"/>
-      <c r="AA38" s="47"/>
-      <c r="AB38" s="47"/>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U38" s="45"/>
+      <c r="V38" s="45"/>
+      <c r="W38" s="45"/>
+      <c r="X38" s="45"/>
+      <c r="Y38" s="45"/>
+      <c r="Z38" s="45"/>
+      <c r="AA38" s="45"/>
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="45"/>
+      <c r="AD38" s="45"/>
+      <c r="AE38" s="45"/>
+      <c r="AF38" s="45"/>
+      <c r="AG38" s="45"/>
+      <c r="AH38" s="45"/>
+      <c r="AI38" s="45"/>
+      <c r="AJ38" s="45"/>
+      <c r="AK38" s="45"/>
+      <c r="AL38" s="45"/>
+      <c r="AM38" s="45"/>
+      <c r="AN38" s="45"/>
+      <c r="AO38" s="45"/>
+      <c r="AP38" s="45"/>
+      <c r="AQ38" s="45"/>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -2219,16 +2789,31 @@
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
       <c r="T39" s="15"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
-      <c r="W39" s="47"/>
-      <c r="X39" s="47"/>
-      <c r="Y39" s="47"/>
-      <c r="Z39" s="47"/>
-      <c r="AA39" s="47"/>
-      <c r="AB39" s="47"/>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U39" s="45"/>
+      <c r="V39" s="45"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="45"/>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="45"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="45"/>
+      <c r="AD39" s="45"/>
+      <c r="AE39" s="45"/>
+      <c r="AF39" s="45"/>
+      <c r="AG39" s="45"/>
+      <c r="AH39" s="45"/>
+      <c r="AI39" s="45"/>
+      <c r="AJ39" s="45"/>
+      <c r="AK39" s="45"/>
+      <c r="AL39" s="45"/>
+      <c r="AM39" s="45"/>
+      <c r="AN39" s="45"/>
+      <c r="AO39" s="45"/>
+      <c r="AP39" s="45"/>
+      <c r="AQ39" s="45"/>
+    </row>
+    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -2249,16 +2834,31 @@
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
       <c r="T40" s="15"/>
-      <c r="U40" s="47"/>
-      <c r="V40" s="47"/>
-      <c r="W40" s="47"/>
-      <c r="X40" s="47"/>
-      <c r="Y40" s="47"/>
-      <c r="Z40" s="47"/>
-      <c r="AA40" s="47"/>
-      <c r="AB40" s="47"/>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U40" s="45"/>
+      <c r="V40" s="45"/>
+      <c r="W40" s="45"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="45"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="45"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="45"/>
+      <c r="AD40" s="45"/>
+      <c r="AE40" s="45"/>
+      <c r="AF40" s="45"/>
+      <c r="AG40" s="45"/>
+      <c r="AH40" s="45"/>
+      <c r="AI40" s="45"/>
+      <c r="AJ40" s="45"/>
+      <c r="AK40" s="45"/>
+      <c r="AL40" s="45"/>
+      <c r="AM40" s="45"/>
+      <c r="AN40" s="45"/>
+      <c r="AO40" s="45"/>
+      <c r="AP40" s="45"/>
+      <c r="AQ40" s="45"/>
+    </row>
+    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -2279,16 +2879,31 @@
       <c r="R41" s="15"/>
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
-      <c r="U41" s="47"/>
-      <c r="V41" s="47"/>
-      <c r="W41" s="47"/>
-      <c r="X41" s="47"/>
-      <c r="Y41" s="47"/>
-      <c r="Z41" s="47"/>
-      <c r="AA41" s="47"/>
-      <c r="AB41" s="47"/>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U41" s="45"/>
+      <c r="V41" s="45"/>
+      <c r="W41" s="45"/>
+      <c r="X41" s="45"/>
+      <c r="Y41" s="45"/>
+      <c r="Z41" s="45"/>
+      <c r="AA41" s="45"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="45"/>
+      <c r="AD41" s="45"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="45"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="45"/>
+      <c r="AI41" s="45"/>
+      <c r="AJ41" s="45"/>
+      <c r="AK41" s="45"/>
+      <c r="AL41" s="45"/>
+      <c r="AM41" s="45"/>
+      <c r="AN41" s="45"/>
+      <c r="AO41" s="45"/>
+      <c r="AP41" s="45"/>
+      <c r="AQ41" s="45"/>
+    </row>
+    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -2309,8 +2924,31 @@
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
       <c r="T42" s="15"/>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U42" s="45"/>
+      <c r="V42" s="45"/>
+      <c r="W42" s="45"/>
+      <c r="X42" s="45"/>
+      <c r="Y42" s="45"/>
+      <c r="Z42" s="45"/>
+      <c r="AA42" s="45"/>
+      <c r="AB42" s="45"/>
+      <c r="AC42" s="45"/>
+      <c r="AD42" s="45"/>
+      <c r="AE42" s="45"/>
+      <c r="AF42" s="45"/>
+      <c r="AG42" s="45"/>
+      <c r="AH42" s="45"/>
+      <c r="AI42" s="45"/>
+      <c r="AJ42" s="45"/>
+      <c r="AK42" s="45"/>
+      <c r="AL42" s="45"/>
+      <c r="AM42" s="45"/>
+      <c r="AN42" s="45"/>
+      <c r="AO42" s="45"/>
+      <c r="AP42" s="45"/>
+      <c r="AQ42" s="45"/>
+    </row>
+    <row r="43" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2331,8 +2969,31 @@
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>
       <c r="T43" s="15"/>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U43" s="45"/>
+      <c r="V43" s="45"/>
+      <c r="W43" s="45"/>
+      <c r="X43" s="45"/>
+      <c r="Y43" s="45"/>
+      <c r="Z43" s="45"/>
+      <c r="AA43" s="45"/>
+      <c r="AB43" s="45"/>
+      <c r="AC43" s="45"/>
+      <c r="AD43" s="45"/>
+      <c r="AE43" s="45"/>
+      <c r="AF43" s="45"/>
+      <c r="AG43" s="45"/>
+      <c r="AH43" s="45"/>
+      <c r="AI43" s="45"/>
+      <c r="AJ43" s="45"/>
+      <c r="AK43" s="45"/>
+      <c r="AL43" s="45"/>
+      <c r="AM43" s="45"/>
+      <c r="AN43" s="45"/>
+      <c r="AO43" s="45"/>
+      <c r="AP43" s="45"/>
+      <c r="AQ43" s="45"/>
+    </row>
+    <row r="44" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2353,8 +3014,31 @@
       <c r="R44" s="15"/>
       <c r="S44" s="15"/>
       <c r="T44" s="15"/>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U44" s="45"/>
+      <c r="V44" s="45"/>
+      <c r="W44" s="45"/>
+      <c r="X44" s="45"/>
+      <c r="Y44" s="45"/>
+      <c r="Z44" s="45"/>
+      <c r="AA44" s="45"/>
+      <c r="AB44" s="45"/>
+      <c r="AC44" s="45"/>
+      <c r="AD44" s="45"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="45"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="45"/>
+      <c r="AI44" s="45"/>
+      <c r="AJ44" s="45"/>
+      <c r="AK44" s="45"/>
+      <c r="AL44" s="45"/>
+      <c r="AM44" s="45"/>
+      <c r="AN44" s="45"/>
+      <c r="AO44" s="45"/>
+      <c r="AP44" s="45"/>
+      <c r="AQ44" s="45"/>
+    </row>
+    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2375,8 +3059,31 @@
       <c r="R45" s="15"/>
       <c r="S45" s="15"/>
       <c r="T45" s="15"/>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U45" s="45"/>
+      <c r="V45" s="45"/>
+      <c r="W45" s="45"/>
+      <c r="X45" s="45"/>
+      <c r="Y45" s="45"/>
+      <c r="Z45" s="45"/>
+      <c r="AA45" s="45"/>
+      <c r="AB45" s="45"/>
+      <c r="AC45" s="45"/>
+      <c r="AD45" s="45"/>
+      <c r="AE45" s="45"/>
+      <c r="AF45" s="45"/>
+      <c r="AG45" s="45"/>
+      <c r="AH45" s="45"/>
+      <c r="AI45" s="45"/>
+      <c r="AJ45" s="45"/>
+      <c r="AK45" s="45"/>
+      <c r="AL45" s="45"/>
+      <c r="AM45" s="45"/>
+      <c r="AN45" s="45"/>
+      <c r="AO45" s="45"/>
+      <c r="AP45" s="45"/>
+      <c r="AQ45" s="45"/>
+    </row>
+    <row r="46" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2397,8 +3104,31 @@
       <c r="R46" s="15"/>
       <c r="S46" s="15"/>
       <c r="T46" s="15"/>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U46" s="45"/>
+      <c r="V46" s="45"/>
+      <c r="W46" s="45"/>
+      <c r="X46" s="45"/>
+      <c r="Y46" s="45"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="45"/>
+      <c r="AB46" s="45"/>
+      <c r="AC46" s="45"/>
+      <c r="AD46" s="45"/>
+      <c r="AE46" s="45"/>
+      <c r="AF46" s="45"/>
+      <c r="AG46" s="45"/>
+      <c r="AH46" s="45"/>
+      <c r="AI46" s="45"/>
+      <c r="AJ46" s="45"/>
+      <c r="AK46" s="45"/>
+      <c r="AL46" s="45"/>
+      <c r="AM46" s="45"/>
+      <c r="AN46" s="45"/>
+      <c r="AO46" s="45"/>
+      <c r="AP46" s="45"/>
+      <c r="AQ46" s="45"/>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2419,8 +3149,31 @@
       <c r="R47" s="15"/>
       <c r="S47" s="15"/>
       <c r="T47" s="15"/>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="U47" s="45"/>
+      <c r="V47" s="45"/>
+      <c r="W47" s="45"/>
+      <c r="X47" s="45"/>
+      <c r="Y47" s="45"/>
+      <c r="Z47" s="45"/>
+      <c r="AA47" s="45"/>
+      <c r="AB47" s="45"/>
+      <c r="AC47" s="45"/>
+      <c r="AD47" s="45"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="45"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="45"/>
+      <c r="AI47" s="45"/>
+      <c r="AJ47" s="45"/>
+      <c r="AK47" s="45"/>
+      <c r="AL47" s="45"/>
+      <c r="AM47" s="45"/>
+      <c r="AN47" s="45"/>
+      <c r="AO47" s="45"/>
+      <c r="AP47" s="45"/>
+      <c r="AQ47" s="45"/>
+    </row>
+    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2441,8 +3194,31 @@
       <c r="R48" s="15"/>
       <c r="S48" s="15"/>
       <c r="T48" s="15"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U48" s="45"/>
+      <c r="V48" s="45"/>
+      <c r="W48" s="45"/>
+      <c r="X48" s="45"/>
+      <c r="Y48" s="45"/>
+      <c r="Z48" s="45"/>
+      <c r="AA48" s="45"/>
+      <c r="AB48" s="45"/>
+      <c r="AC48" s="45"/>
+      <c r="AD48" s="45"/>
+      <c r="AE48" s="45"/>
+      <c r="AF48" s="45"/>
+      <c r="AG48" s="45"/>
+      <c r="AH48" s="45"/>
+      <c r="AI48" s="45"/>
+      <c r="AJ48" s="45"/>
+      <c r="AK48" s="45"/>
+      <c r="AL48" s="45"/>
+      <c r="AM48" s="45"/>
+      <c r="AN48" s="45"/>
+      <c r="AO48" s="45"/>
+      <c r="AP48" s="45"/>
+      <c r="AQ48" s="45"/>
+    </row>
+    <row r="49" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2463,8 +3239,31 @@
       <c r="R49" s="15"/>
       <c r="S49" s="15"/>
       <c r="T49" s="15"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U49" s="45"/>
+      <c r="V49" s="45"/>
+      <c r="W49" s="45"/>
+      <c r="X49" s="45"/>
+      <c r="Y49" s="45"/>
+      <c r="Z49" s="45"/>
+      <c r="AA49" s="45"/>
+      <c r="AB49" s="45"/>
+      <c r="AC49" s="45"/>
+      <c r="AD49" s="45"/>
+      <c r="AE49" s="45"/>
+      <c r="AF49" s="45"/>
+      <c r="AG49" s="45"/>
+      <c r="AH49" s="45"/>
+      <c r="AI49" s="45"/>
+      <c r="AJ49" s="45"/>
+      <c r="AK49" s="45"/>
+      <c r="AL49" s="45"/>
+      <c r="AM49" s="45"/>
+      <c r="AN49" s="45"/>
+      <c r="AO49" s="45"/>
+      <c r="AP49" s="45"/>
+      <c r="AQ49" s="45"/>
+    </row>
+    <row r="50" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2485,8 +3284,31 @@
       <c r="R50" s="15"/>
       <c r="S50" s="15"/>
       <c r="T50" s="15"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U50" s="45"/>
+      <c r="V50" s="45"/>
+      <c r="W50" s="45"/>
+      <c r="X50" s="45"/>
+      <c r="Y50" s="45"/>
+      <c r="Z50" s="45"/>
+      <c r="AA50" s="45"/>
+      <c r="AB50" s="45"/>
+      <c r="AC50" s="45"/>
+      <c r="AD50" s="45"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="45"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="45"/>
+      <c r="AI50" s="45"/>
+      <c r="AJ50" s="45"/>
+      <c r="AK50" s="45"/>
+      <c r="AL50" s="45"/>
+      <c r="AM50" s="45"/>
+      <c r="AN50" s="45"/>
+      <c r="AO50" s="45"/>
+      <c r="AP50" s="45"/>
+      <c r="AQ50" s="45"/>
+    </row>
+    <row r="51" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2507,8 +3329,31 @@
       <c r="R51" s="15"/>
       <c r="S51" s="15"/>
       <c r="T51" s="15"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U51" s="45"/>
+      <c r="V51" s="45"/>
+      <c r="W51" s="45"/>
+      <c r="X51" s="45"/>
+      <c r="Y51" s="45"/>
+      <c r="Z51" s="45"/>
+      <c r="AA51" s="45"/>
+      <c r="AB51" s="45"/>
+      <c r="AC51" s="45"/>
+      <c r="AD51" s="45"/>
+      <c r="AE51" s="45"/>
+      <c r="AF51" s="45"/>
+      <c r="AG51" s="45"/>
+      <c r="AH51" s="45"/>
+      <c r="AI51" s="45"/>
+      <c r="AJ51" s="45"/>
+      <c r="AK51" s="45"/>
+      <c r="AL51" s="45"/>
+      <c r="AM51" s="45"/>
+      <c r="AN51" s="45"/>
+      <c r="AO51" s="45"/>
+      <c r="AP51" s="45"/>
+      <c r="AQ51" s="45"/>
+    </row>
+    <row r="52" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2529,8 +3374,31 @@
       <c r="R52" s="15"/>
       <c r="S52" s="15"/>
       <c r="T52" s="15"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U52" s="45"/>
+      <c r="V52" s="45"/>
+      <c r="W52" s="45"/>
+      <c r="X52" s="45"/>
+      <c r="Y52" s="45"/>
+      <c r="Z52" s="45"/>
+      <c r="AA52" s="45"/>
+      <c r="AB52" s="45"/>
+      <c r="AC52" s="45"/>
+      <c r="AD52" s="45"/>
+      <c r="AE52" s="45"/>
+      <c r="AF52" s="45"/>
+      <c r="AG52" s="45"/>
+      <c r="AH52" s="45"/>
+      <c r="AI52" s="45"/>
+      <c r="AJ52" s="45"/>
+      <c r="AK52" s="45"/>
+      <c r="AL52" s="45"/>
+      <c r="AM52" s="45"/>
+      <c r="AN52" s="45"/>
+      <c r="AO52" s="45"/>
+      <c r="AP52" s="45"/>
+      <c r="AQ52" s="45"/>
+    </row>
+    <row r="53" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2551,8 +3419,31 @@
       <c r="R53" s="15"/>
       <c r="S53" s="15"/>
       <c r="T53" s="15"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U53" s="45"/>
+      <c r="V53" s="45"/>
+      <c r="W53" s="45"/>
+      <c r="X53" s="45"/>
+      <c r="Y53" s="45"/>
+      <c r="Z53" s="45"/>
+      <c r="AA53" s="45"/>
+      <c r="AB53" s="45"/>
+      <c r="AC53" s="45"/>
+      <c r="AD53" s="45"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="45"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="45"/>
+      <c r="AI53" s="45"/>
+      <c r="AJ53" s="45"/>
+      <c r="AK53" s="45"/>
+      <c r="AL53" s="45"/>
+      <c r="AM53" s="45"/>
+      <c r="AN53" s="45"/>
+      <c r="AO53" s="45"/>
+      <c r="AP53" s="45"/>
+      <c r="AQ53" s="45"/>
+    </row>
+    <row r="54" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2573,8 +3464,31 @@
       <c r="R54" s="15"/>
       <c r="S54" s="15"/>
       <c r="T54" s="15"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U54" s="45"/>
+      <c r="V54" s="45"/>
+      <c r="W54" s="45"/>
+      <c r="X54" s="45"/>
+      <c r="Y54" s="45"/>
+      <c r="Z54" s="45"/>
+      <c r="AA54" s="45"/>
+      <c r="AB54" s="45"/>
+      <c r="AC54" s="45"/>
+      <c r="AD54" s="45"/>
+      <c r="AE54" s="45"/>
+      <c r="AF54" s="45"/>
+      <c r="AG54" s="45"/>
+      <c r="AH54" s="45"/>
+      <c r="AI54" s="45"/>
+      <c r="AJ54" s="45"/>
+      <c r="AK54" s="45"/>
+      <c r="AL54" s="45"/>
+      <c r="AM54" s="45"/>
+      <c r="AN54" s="45"/>
+      <c r="AO54" s="45"/>
+      <c r="AP54" s="45"/>
+      <c r="AQ54" s="45"/>
+    </row>
+    <row r="55" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2595,8 +3509,31 @@
       <c r="R55" s="15"/>
       <c r="S55" s="15"/>
       <c r="T55" s="15"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U55" s="45"/>
+      <c r="V55" s="45"/>
+      <c r="W55" s="45"/>
+      <c r="X55" s="45"/>
+      <c r="Y55" s="45"/>
+      <c r="Z55" s="45"/>
+      <c r="AA55" s="45"/>
+      <c r="AB55" s="45"/>
+      <c r="AC55" s="45"/>
+      <c r="AD55" s="45"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="45"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="45"/>
+      <c r="AI55" s="45"/>
+      <c r="AJ55" s="45"/>
+      <c r="AK55" s="45"/>
+      <c r="AL55" s="45"/>
+      <c r="AM55" s="45"/>
+      <c r="AN55" s="45"/>
+      <c r="AO55" s="45"/>
+      <c r="AP55" s="45"/>
+      <c r="AQ55" s="45"/>
+    </row>
+    <row r="56" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2617,8 +3554,31 @@
       <c r="R56" s="15"/>
       <c r="S56" s="15"/>
       <c r="T56" s="15"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U56" s="45"/>
+      <c r="V56" s="45"/>
+      <c r="W56" s="45"/>
+      <c r="X56" s="45"/>
+      <c r="Y56" s="45"/>
+      <c r="Z56" s="45"/>
+      <c r="AA56" s="45"/>
+      <c r="AB56" s="45"/>
+      <c r="AC56" s="45"/>
+      <c r="AD56" s="45"/>
+      <c r="AE56" s="45"/>
+      <c r="AF56" s="45"/>
+      <c r="AG56" s="45"/>
+      <c r="AH56" s="45"/>
+      <c r="AI56" s="45"/>
+      <c r="AJ56" s="45"/>
+      <c r="AK56" s="45"/>
+      <c r="AL56" s="45"/>
+      <c r="AM56" s="45"/>
+      <c r="AN56" s="45"/>
+      <c r="AO56" s="45"/>
+      <c r="AP56" s="45"/>
+      <c r="AQ56" s="45"/>
+    </row>
+    <row r="57" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2639,8 +3599,31 @@
       <c r="R57" s="15"/>
       <c r="S57" s="15"/>
       <c r="T57" s="15"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U57" s="45"/>
+      <c r="V57" s="45"/>
+      <c r="W57" s="45"/>
+      <c r="X57" s="45"/>
+      <c r="Y57" s="45"/>
+      <c r="Z57" s="45"/>
+      <c r="AA57" s="45"/>
+      <c r="AB57" s="45"/>
+      <c r="AC57" s="45"/>
+      <c r="AD57" s="45"/>
+      <c r="AE57" s="45"/>
+      <c r="AF57" s="45"/>
+      <c r="AG57" s="45"/>
+      <c r="AH57" s="45"/>
+      <c r="AI57" s="45"/>
+      <c r="AJ57" s="45"/>
+      <c r="AK57" s="45"/>
+      <c r="AL57" s="45"/>
+      <c r="AM57" s="45"/>
+      <c r="AN57" s="45"/>
+      <c r="AO57" s="45"/>
+      <c r="AP57" s="45"/>
+      <c r="AQ57" s="45"/>
+    </row>
+    <row r="58" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2661,8 +3644,31 @@
       <c r="R58" s="15"/>
       <c r="S58" s="15"/>
       <c r="T58" s="15"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U58" s="45"/>
+      <c r="V58" s="45"/>
+      <c r="W58" s="45"/>
+      <c r="X58" s="45"/>
+      <c r="Y58" s="45"/>
+      <c r="Z58" s="45"/>
+      <c r="AA58" s="45"/>
+      <c r="AB58" s="45"/>
+      <c r="AC58" s="45"/>
+      <c r="AD58" s="45"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="45"/>
+      <c r="AJ58" s="45"/>
+      <c r="AK58" s="45"/>
+      <c r="AL58" s="45"/>
+      <c r="AM58" s="45"/>
+      <c r="AN58" s="45"/>
+      <c r="AO58" s="45"/>
+      <c r="AP58" s="45"/>
+      <c r="AQ58" s="45"/>
+    </row>
+    <row r="59" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2683,8 +3689,31 @@
       <c r="R59" s="15"/>
       <c r="S59" s="15"/>
       <c r="T59" s="15"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U59" s="45"/>
+      <c r="V59" s="45"/>
+      <c r="W59" s="45"/>
+      <c r="X59" s="45"/>
+      <c r="Y59" s="45"/>
+      <c r="Z59" s="45"/>
+      <c r="AA59" s="45"/>
+      <c r="AB59" s="45"/>
+      <c r="AC59" s="45"/>
+      <c r="AD59" s="45"/>
+      <c r="AE59" s="45"/>
+      <c r="AF59" s="45"/>
+      <c r="AG59" s="45"/>
+      <c r="AH59" s="45"/>
+      <c r="AI59" s="45"/>
+      <c r="AJ59" s="45"/>
+      <c r="AK59" s="45"/>
+      <c r="AL59" s="45"/>
+      <c r="AM59" s="45"/>
+      <c r="AN59" s="45"/>
+      <c r="AO59" s="45"/>
+      <c r="AP59" s="45"/>
+      <c r="AQ59" s="45"/>
+    </row>
+    <row r="60" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2705,8 +3734,31 @@
       <c r="R60" s="15"/>
       <c r="S60" s="15"/>
       <c r="T60" s="15"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U60" s="45"/>
+      <c r="V60" s="45"/>
+      <c r="W60" s="45"/>
+      <c r="X60" s="45"/>
+      <c r="Y60" s="45"/>
+      <c r="Z60" s="45"/>
+      <c r="AA60" s="45"/>
+      <c r="AB60" s="45"/>
+      <c r="AC60" s="45"/>
+      <c r="AD60" s="45"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="45"/>
+      <c r="AJ60" s="45"/>
+      <c r="AK60" s="45"/>
+      <c r="AL60" s="45"/>
+      <c r="AM60" s="45"/>
+      <c r="AN60" s="45"/>
+      <c r="AO60" s="45"/>
+      <c r="AP60" s="45"/>
+      <c r="AQ60" s="45"/>
+    </row>
+    <row r="61" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2727,8 +3779,31 @@
       <c r="R61" s="15"/>
       <c r="S61" s="15"/>
       <c r="T61" s="15"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U61" s="45"/>
+      <c r="V61" s="45"/>
+      <c r="W61" s="45"/>
+      <c r="X61" s="45"/>
+      <c r="Y61" s="45"/>
+      <c r="Z61" s="45"/>
+      <c r="AA61" s="45"/>
+      <c r="AB61" s="45"/>
+      <c r="AC61" s="45"/>
+      <c r="AD61" s="45"/>
+      <c r="AE61" s="45"/>
+      <c r="AF61" s="45"/>
+      <c r="AG61" s="45"/>
+      <c r="AH61" s="45"/>
+      <c r="AI61" s="45"/>
+      <c r="AJ61" s="45"/>
+      <c r="AK61" s="45"/>
+      <c r="AL61" s="45"/>
+      <c r="AM61" s="45"/>
+      <c r="AN61" s="45"/>
+      <c r="AO61" s="45"/>
+      <c r="AP61" s="45"/>
+      <c r="AQ61" s="45"/>
+    </row>
+    <row r="62" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2749,8 +3824,31 @@
       <c r="R62" s="15"/>
       <c r="S62" s="15"/>
       <c r="T62" s="15"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U62" s="45"/>
+      <c r="V62" s="45"/>
+      <c r="W62" s="45"/>
+      <c r="X62" s="45"/>
+      <c r="Y62" s="45"/>
+      <c r="Z62" s="45"/>
+      <c r="AA62" s="45"/>
+      <c r="AB62" s="45"/>
+      <c r="AC62" s="45"/>
+      <c r="AD62" s="45"/>
+      <c r="AE62" s="45"/>
+      <c r="AF62" s="45"/>
+      <c r="AG62" s="45"/>
+      <c r="AH62" s="45"/>
+      <c r="AI62" s="45"/>
+      <c r="AJ62" s="45"/>
+      <c r="AK62" s="45"/>
+      <c r="AL62" s="45"/>
+      <c r="AM62" s="45"/>
+      <c r="AN62" s="45"/>
+      <c r="AO62" s="45"/>
+      <c r="AP62" s="45"/>
+      <c r="AQ62" s="45"/>
+    </row>
+    <row r="63" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2771,8 +3869,31 @@
       <c r="R63" s="15"/>
       <c r="S63" s="15"/>
       <c r="T63" s="15"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U63" s="45"/>
+      <c r="V63" s="45"/>
+      <c r="W63" s="45"/>
+      <c r="X63" s="45"/>
+      <c r="Y63" s="45"/>
+      <c r="Z63" s="45"/>
+      <c r="AA63" s="45"/>
+      <c r="AB63" s="45"/>
+      <c r="AC63" s="45"/>
+      <c r="AD63" s="45"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="45"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="45"/>
+      <c r="AI63" s="45"/>
+      <c r="AJ63" s="45"/>
+      <c r="AK63" s="45"/>
+      <c r="AL63" s="45"/>
+      <c r="AM63" s="45"/>
+      <c r="AN63" s="45"/>
+      <c r="AO63" s="45"/>
+      <c r="AP63" s="45"/>
+      <c r="AQ63" s="45"/>
+    </row>
+    <row r="64" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2793,8 +3914,31 @@
       <c r="R64" s="15"/>
       <c r="S64" s="15"/>
       <c r="T64" s="15"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U64" s="45"/>
+      <c r="V64" s="45"/>
+      <c r="W64" s="45"/>
+      <c r="X64" s="45"/>
+      <c r="Y64" s="45"/>
+      <c r="Z64" s="45"/>
+      <c r="AA64" s="45"/>
+      <c r="AB64" s="45"/>
+      <c r="AC64" s="45"/>
+      <c r="AD64" s="45"/>
+      <c r="AE64" s="45"/>
+      <c r="AF64" s="45"/>
+      <c r="AG64" s="45"/>
+      <c r="AH64" s="45"/>
+      <c r="AI64" s="45"/>
+      <c r="AJ64" s="45"/>
+      <c r="AK64" s="45"/>
+      <c r="AL64" s="45"/>
+      <c r="AM64" s="45"/>
+      <c r="AN64" s="45"/>
+      <c r="AO64" s="45"/>
+      <c r="AP64" s="45"/>
+      <c r="AQ64" s="45"/>
+    </row>
+    <row r="65" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2815,8 +3959,31 @@
       <c r="R65" s="15"/>
       <c r="S65" s="15"/>
       <c r="T65" s="15"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U65" s="45"/>
+      <c r="V65" s="45"/>
+      <c r="W65" s="45"/>
+      <c r="X65" s="45"/>
+      <c r="Y65" s="45"/>
+      <c r="Z65" s="45"/>
+      <c r="AA65" s="45"/>
+      <c r="AB65" s="45"/>
+      <c r="AC65" s="45"/>
+      <c r="AD65" s="45"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="45"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="45"/>
+      <c r="AI65" s="45"/>
+      <c r="AJ65" s="45"/>
+      <c r="AK65" s="45"/>
+      <c r="AL65" s="45"/>
+      <c r="AM65" s="45"/>
+      <c r="AN65" s="45"/>
+      <c r="AO65" s="45"/>
+      <c r="AP65" s="45"/>
+      <c r="AQ65" s="45"/>
+    </row>
+    <row r="66" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2837,8 +4004,31 @@
       <c r="R66" s="15"/>
       <c r="S66" s="15"/>
       <c r="T66" s="15"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U66" s="45"/>
+      <c r="V66" s="45"/>
+      <c r="W66" s="45"/>
+      <c r="X66" s="45"/>
+      <c r="Y66" s="45"/>
+      <c r="Z66" s="45"/>
+      <c r="AA66" s="45"/>
+      <c r="AB66" s="45"/>
+      <c r="AC66" s="45"/>
+      <c r="AD66" s="45"/>
+      <c r="AE66" s="45"/>
+      <c r="AF66" s="45"/>
+      <c r="AG66" s="45"/>
+      <c r="AH66" s="45"/>
+      <c r="AI66" s="45"/>
+      <c r="AJ66" s="45"/>
+      <c r="AK66" s="45"/>
+      <c r="AL66" s="45"/>
+      <c r="AM66" s="45"/>
+      <c r="AN66" s="45"/>
+      <c r="AO66" s="45"/>
+      <c r="AP66" s="45"/>
+      <c r="AQ66" s="45"/>
+    </row>
+    <row r="67" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2859,8 +4049,31 @@
       <c r="R67" s="15"/>
       <c r="S67" s="15"/>
       <c r="T67" s="15"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U67" s="45"/>
+      <c r="V67" s="45"/>
+      <c r="W67" s="45"/>
+      <c r="X67" s="45"/>
+      <c r="Y67" s="45"/>
+      <c r="Z67" s="45"/>
+      <c r="AA67" s="45"/>
+      <c r="AB67" s="45"/>
+      <c r="AC67" s="45"/>
+      <c r="AD67" s="45"/>
+      <c r="AE67" s="45"/>
+      <c r="AF67" s="45"/>
+      <c r="AG67" s="45"/>
+      <c r="AH67" s="45"/>
+      <c r="AI67" s="45"/>
+      <c r="AJ67" s="45"/>
+      <c r="AK67" s="45"/>
+      <c r="AL67" s="45"/>
+      <c r="AM67" s="45"/>
+      <c r="AN67" s="45"/>
+      <c r="AO67" s="45"/>
+      <c r="AP67" s="45"/>
+      <c r="AQ67" s="45"/>
+    </row>
+    <row r="68" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2881,8 +4094,31 @@
       <c r="R68" s="15"/>
       <c r="S68" s="15"/>
       <c r="T68" s="15"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U68" s="45"/>
+      <c r="V68" s="45"/>
+      <c r="W68" s="45"/>
+      <c r="X68" s="45"/>
+      <c r="Y68" s="45"/>
+      <c r="Z68" s="45"/>
+      <c r="AA68" s="45"/>
+      <c r="AB68" s="45"/>
+      <c r="AC68" s="45"/>
+      <c r="AD68" s="45"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="45"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="45"/>
+      <c r="AI68" s="45"/>
+      <c r="AJ68" s="45"/>
+      <c r="AK68" s="45"/>
+      <c r="AL68" s="45"/>
+      <c r="AM68" s="45"/>
+      <c r="AN68" s="45"/>
+      <c r="AO68" s="45"/>
+      <c r="AP68" s="45"/>
+      <c r="AQ68" s="45"/>
+    </row>
+    <row r="69" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2903,8 +4139,31 @@
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
       <c r="T69" s="15"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U69" s="45"/>
+      <c r="V69" s="45"/>
+      <c r="W69" s="45"/>
+      <c r="X69" s="45"/>
+      <c r="Y69" s="45"/>
+      <c r="Z69" s="45"/>
+      <c r="AA69" s="45"/>
+      <c r="AB69" s="45"/>
+      <c r="AC69" s="45"/>
+      <c r="AD69" s="45"/>
+      <c r="AE69" s="45"/>
+      <c r="AF69" s="45"/>
+      <c r="AG69" s="45"/>
+      <c r="AH69" s="45"/>
+      <c r="AI69" s="45"/>
+      <c r="AJ69" s="45"/>
+      <c r="AK69" s="45"/>
+      <c r="AL69" s="45"/>
+      <c r="AM69" s="45"/>
+      <c r="AN69" s="45"/>
+      <c r="AO69" s="45"/>
+      <c r="AP69" s="45"/>
+      <c r="AQ69" s="45"/>
+    </row>
+    <row r="70" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2925,8 +4184,31 @@
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
       <c r="T70" s="15"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U70" s="45"/>
+      <c r="V70" s="45"/>
+      <c r="W70" s="45"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="45"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="45"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="45"/>
+      <c r="AD70" s="45"/>
+      <c r="AE70" s="45"/>
+      <c r="AF70" s="45"/>
+      <c r="AG70" s="45"/>
+      <c r="AH70" s="45"/>
+      <c r="AI70" s="45"/>
+      <c r="AJ70" s="45"/>
+      <c r="AK70" s="45"/>
+      <c r="AL70" s="45"/>
+      <c r="AM70" s="45"/>
+      <c r="AN70" s="45"/>
+      <c r="AO70" s="45"/>
+      <c r="AP70" s="45"/>
+      <c r="AQ70" s="45"/>
+    </row>
+    <row r="71" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2947,8 +4229,31 @@
       <c r="R71" s="15"/>
       <c r="S71" s="15"/>
       <c r="T71" s="15"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U71" s="45"/>
+      <c r="V71" s="45"/>
+      <c r="W71" s="45"/>
+      <c r="X71" s="45"/>
+      <c r="Y71" s="45"/>
+      <c r="Z71" s="45"/>
+      <c r="AA71" s="45"/>
+      <c r="AB71" s="45"/>
+      <c r="AC71" s="45"/>
+      <c r="AD71" s="45"/>
+      <c r="AE71" s="45"/>
+      <c r="AF71" s="45"/>
+      <c r="AG71" s="45"/>
+      <c r="AH71" s="45"/>
+      <c r="AI71" s="45"/>
+      <c r="AJ71" s="45"/>
+      <c r="AK71" s="45"/>
+      <c r="AL71" s="45"/>
+      <c r="AM71" s="45"/>
+      <c r="AN71" s="45"/>
+      <c r="AO71" s="45"/>
+      <c r="AP71" s="45"/>
+      <c r="AQ71" s="45"/>
+    </row>
+    <row r="72" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -2969,8 +4274,31 @@
       <c r="R72" s="15"/>
       <c r="S72" s="15"/>
       <c r="T72" s="15"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U72" s="45"/>
+      <c r="V72" s="45"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
+      <c r="Y72" s="45"/>
+      <c r="Z72" s="45"/>
+      <c r="AA72" s="45"/>
+      <c r="AB72" s="45"/>
+      <c r="AC72" s="45"/>
+      <c r="AD72" s="45"/>
+      <c r="AE72" s="45"/>
+      <c r="AF72" s="45"/>
+      <c r="AG72" s="45"/>
+      <c r="AH72" s="45"/>
+      <c r="AI72" s="45"/>
+      <c r="AJ72" s="45"/>
+      <c r="AK72" s="45"/>
+      <c r="AL72" s="45"/>
+      <c r="AM72" s="45"/>
+      <c r="AN72" s="45"/>
+      <c r="AO72" s="45"/>
+      <c r="AP72" s="45"/>
+      <c r="AQ72" s="45"/>
+    </row>
+    <row r="73" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -2991,8 +4319,31 @@
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
       <c r="T73" s="15"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U73" s="45"/>
+      <c r="V73" s="45"/>
+      <c r="W73" s="45"/>
+      <c r="X73" s="45"/>
+      <c r="Y73" s="45"/>
+      <c r="Z73" s="45"/>
+      <c r="AA73" s="45"/>
+      <c r="AB73" s="45"/>
+      <c r="AC73" s="45"/>
+      <c r="AD73" s="45"/>
+      <c r="AE73" s="45"/>
+      <c r="AF73" s="45"/>
+      <c r="AG73" s="45"/>
+      <c r="AH73" s="45"/>
+      <c r="AI73" s="45"/>
+      <c r="AJ73" s="45"/>
+      <c r="AK73" s="45"/>
+      <c r="AL73" s="45"/>
+      <c r="AM73" s="45"/>
+      <c r="AN73" s="45"/>
+      <c r="AO73" s="45"/>
+      <c r="AP73" s="45"/>
+      <c r="AQ73" s="45"/>
+    </row>
+    <row r="74" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3013,8 +4364,31 @@
       <c r="R74" s="15"/>
       <c r="S74" s="15"/>
       <c r="T74" s="15"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U74" s="45"/>
+      <c r="V74" s="45"/>
+      <c r="W74" s="45"/>
+      <c r="X74" s="45"/>
+      <c r="Y74" s="45"/>
+      <c r="Z74" s="45"/>
+      <c r="AA74" s="45"/>
+      <c r="AB74" s="45"/>
+      <c r="AC74" s="45"/>
+      <c r="AD74" s="45"/>
+      <c r="AE74" s="45"/>
+      <c r="AF74" s="45"/>
+      <c r="AG74" s="45"/>
+      <c r="AH74" s="45"/>
+      <c r="AI74" s="45"/>
+      <c r="AJ74" s="45"/>
+      <c r="AK74" s="45"/>
+      <c r="AL74" s="45"/>
+      <c r="AM74" s="45"/>
+      <c r="AN74" s="45"/>
+      <c r="AO74" s="45"/>
+      <c r="AP74" s="45"/>
+      <c r="AQ74" s="45"/>
+    </row>
+    <row r="75" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3035,8 +4409,31 @@
       <c r="R75" s="15"/>
       <c r="S75" s="15"/>
       <c r="T75" s="15"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U75" s="45"/>
+      <c r="V75" s="45"/>
+      <c r="W75" s="45"/>
+      <c r="X75" s="45"/>
+      <c r="Y75" s="45"/>
+      <c r="Z75" s="45"/>
+      <c r="AA75" s="45"/>
+      <c r="AB75" s="45"/>
+      <c r="AC75" s="45"/>
+      <c r="AD75" s="45"/>
+      <c r="AE75" s="45"/>
+      <c r="AF75" s="45"/>
+      <c r="AG75" s="45"/>
+      <c r="AH75" s="45"/>
+      <c r="AI75" s="45"/>
+      <c r="AJ75" s="45"/>
+      <c r="AK75" s="45"/>
+      <c r="AL75" s="45"/>
+      <c r="AM75" s="45"/>
+      <c r="AN75" s="45"/>
+      <c r="AO75" s="45"/>
+      <c r="AP75" s="45"/>
+      <c r="AQ75" s="45"/>
+    </row>
+    <row r="76" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3058,7 +4455,7 @@
       <c r="S76" s="15"/>
       <c r="T76" s="15"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3080,7 +4477,7 @@
       <c r="S77" s="15"/>
       <c r="T77" s="15"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3102,7 +4499,7 @@
       <c r="S78" s="15"/>
       <c r="T78" s="15"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3124,7 +4521,7 @@
       <c r="S79" s="15"/>
       <c r="T79" s="15"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>

--- a/Planning_previsionnel.xlsx
+++ b/Planning_previsionnel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antoi\OneDrive\Documents\S8\Projet_Synthese_I4.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3F8087-B2B8-45F3-8233-2615C115B9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D007D7A-14B6-4231-AA1A-F2D11102BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
+    <workbookView xWindow="15" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -490,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -652,6 +652,7 @@
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2472,8 +2473,8 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="6"/>
+      <c r="R30" s="63"/>
+      <c r="S30" s="30"/>
       <c r="T30" s="6"/>
       <c r="U30" s="14"/>
       <c r="V30" s="14"/>

--- a/Planning_previsionnel.xlsx
+++ b/Planning_previsionnel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D007D7A-14B6-4231-AA1A-F2D11102BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C6E03F00-DCAA-4FE6-A67F-FD741686D31C}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -567,6 +567,41 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -618,41 +653,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -991,7 +991,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="34" t="s">
         <v>35</v>
       </c>
       <c r="B1" t="s">
@@ -1045,38 +1045,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59" t="s">
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="60" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60" t="s">
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="59" t="s">
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="59"/>
+      <c r="T1" s="37"/>
       <c r="U1" s="14"/>
       <c r="V1" s="14"/>
       <c r="W1" s="14"/>
@@ -1102,7 +1102,7 @@
       <c r="AQ1" s="14"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
+      <c r="A2" s="38"/>
       <c r="B2" s="4">
         <v>46132</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="51"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1330,7 +1330,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="10"/>
-      <c r="C6" s="52"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -1377,7 +1377,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="52"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1424,8 +1424,8 @@
         <v>14</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="54"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1567,8 +1567,8 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="2"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
@@ -1614,8 +1614,8 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="58"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
       <c r="G12" s="2"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
@@ -1710,8 +1710,8 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -1757,8 +1757,8 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -1900,8 +1900,8 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="6"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="35"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="48"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -1947,8 +1947,8 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="41"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -1996,8 +1996,8 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="35"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="48"/>
       <c r="M20" s="11"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -2043,9 +2043,9 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="41"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="54"/>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
@@ -2090,9 +2090,9 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="54"/>
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
@@ -2234,10 +2234,10 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="28"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="37"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="50"/>
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
@@ -2281,10 +2281,10 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="38"/>
-      <c r="P26" s="38"/>
-      <c r="Q26" s="39"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="52"/>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
@@ -2473,7 +2473,7 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
-      <c r="R30" s="63"/>
+      <c r="R30" s="35"/>
       <c r="S30" s="30"/>
       <c r="T30" s="6"/>
       <c r="U30" s="14"/>
@@ -2564,9 +2564,9 @@
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="44"/>
+      <c r="Q32" s="55"/>
+      <c r="R32" s="56"/>
+      <c r="S32" s="57"/>
       <c r="T32" s="6"/>
       <c r="U32" s="14"/>
       <c r="V32" s="14"/>
@@ -11241,21 +11241,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="N25:Q26"/>
+    <mergeCell ref="K21:M22"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="K20:L20"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="N25:Q26"/>
-    <mergeCell ref="K21:M22"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I18:J19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
